--- a/data/trans_bre/P23_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -4,39</t>
+          <t>-21,03; -4,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 3,07</t>
+          <t>-12,9; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,66; -2,89</t>
+          <t>-17,98; -2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 2,02</t>
+          <t>-12,28; 3,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,02; -12,77</t>
+          <t>-49,86; -12,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 9,59</t>
+          <t>-30,41; 10,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -8,49</t>
+          <t>-45,22; -9,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 8,44</t>
+          <t>-38,09; 14,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -7,9</t>
+          <t>-19,56; -8,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,43; -5,41</t>
+          <t>-17,33; -5,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -8,37</t>
+          <t>-20,22; -7,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -0,95</t>
+          <t>-12,42; -0,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,54; -23,94</t>
+          <t>-50,09; -23,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,12; -14,04</t>
+          <t>-40,78; -14,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,79; -21,5</t>
+          <t>-45,27; -20,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,22; -4,21</t>
+          <t>-42,22; -1,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -7,36</t>
+          <t>-22,84; -7,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,81; -5,32</t>
+          <t>-19,92; -5,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 0,84</t>
+          <t>-12,99; 0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 0,88</t>
+          <t>-11,23; 0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,22; -20,11</t>
+          <t>-47,73; -19,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,55; -14,96</t>
+          <t>-47,95; -15,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 3,67</t>
+          <t>-38,36; 1,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 3,62</t>
+          <t>-41,36; 1,53</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,24; -11,75</t>
+          <t>-25,21; -11,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 1,46</t>
+          <t>-12,32; 0,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -2,0</t>
+          <t>-16,64; -2,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,15; -2,0</t>
+          <t>-18,57; -1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,11; -27,87</t>
+          <t>-52,06; -28,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 5,64</t>
+          <t>-33,99; 2,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,76; -6,22</t>
+          <t>-40,43; -8,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,96; -10,65</t>
+          <t>-63,91; -8,25</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,34; -2,09</t>
+          <t>-20,18; -2,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,52; -2,25</t>
+          <t>-21,1; -1,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,82; -5,46</t>
+          <t>-23,48; -5,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 1,04</t>
+          <t>-10,36; 0,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,24; -6,05</t>
+          <t>-46,44; -6,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,65; -5,48</t>
+          <t>-46,04; -4,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,93; -14,45</t>
+          <t>-52,19; -15,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 7,44</t>
+          <t>-44,64; 5,98</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,13; -15,09</t>
+          <t>-30,33; -14,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 1,27</t>
+          <t>-13,37; 2,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 1,1</t>
+          <t>-15,35; 1,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -2,94</t>
+          <t>-15,96; -2,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,59; -35,44</t>
+          <t>-61,37; -35,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 5,67</t>
+          <t>-39,4; 8,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 3,73</t>
+          <t>-40,32; 4,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,52; -12,39</t>
+          <t>-50,35; -11,94</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,4; -6,82</t>
+          <t>-16,68; -6,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -6,38</t>
+          <t>-16,63; -6,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 0,11</t>
+          <t>-9,79; 0,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,28; -1,63</t>
+          <t>-22,25; -2,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,95; -19,51</t>
+          <t>-42,21; -19,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -17,28</t>
+          <t>-40,15; -17,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 0,32</t>
+          <t>-29,69; 2,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-74,08; -6,93</t>
+          <t>-69,41; -8,27</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -12,06</t>
+          <t>-21,77; -12,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -5,73</t>
+          <t>-15,15; -5,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,03; -1,93</t>
+          <t>-11,24; -1,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 8,82</t>
+          <t>-11,37; 9,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,07; -32,65</t>
+          <t>-51,86; -32,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,91; -17,28</t>
+          <t>-39,19; -17,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,39; -6,6</t>
+          <t>-32,88; -6,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 86,07</t>
+          <t>-41,63; 97,01</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,45; -12,85</t>
+          <t>-17,6; -13,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,09; -7,45</t>
+          <t>-12,05; -7,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -6,3</t>
+          <t>-10,76; -6,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -1,16</t>
+          <t>-9,66; -1,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-42,77; -33,23</t>
+          <t>-42,63; -34,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,88; -21,0</t>
+          <t>-32,09; -21,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,76; -18,77</t>
+          <t>-30,1; -18,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-38,09; -8,97</t>
+          <t>-38,15; -7,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,63</t>
+          <t>-2,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,09%</t>
+          <t>-11,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,03; -4,38</t>
+          <t>-20,55; -4,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 3,85</t>
+          <t>-14,08; 2,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,98; -2,88</t>
+          <t>-18,01; -2,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 3,04</t>
+          <t>-9,0; 3,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,86; -12,44</t>
+          <t>-49,86; -14,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 10,57</t>
+          <t>-33,12; 7,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,22; -9,78</t>
+          <t>-45,0; -6,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 14,54</t>
+          <t>-32,93; 17,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>-6,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-24,84%</t>
+          <t>-26,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,56; -8,13</t>
+          <t>-19,81; -7,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -5,87</t>
+          <t>-18,35; -5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,22; -7,79</t>
+          <t>-20,34; -9,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -0,32</t>
+          <t>-12,57; -1,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -23,92</t>
+          <t>-49,81; -23,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -14,97</t>
+          <t>-41,77; -15,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -20,66</t>
+          <t>-45,54; -22,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,22; -1,39</t>
+          <t>-42,19; -5,67</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,09</t>
+          <t>-7,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-21,67%</t>
+          <t>-27,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,84; -7,42</t>
+          <t>-23,03; -7,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,92; -5,73</t>
+          <t>-20,68; -5,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 0,64</t>
+          <t>-13,13; 1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 0,31</t>
+          <t>-12,72; -1,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,73; -19,38</t>
+          <t>-48,97; -20,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,95; -15,79</t>
+          <t>-49,07; -16,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 1,99</t>
+          <t>-39,43; 5,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 1,53</t>
+          <t>-44,06; -6,98</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,04</t>
+          <t>-5,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,89%</t>
+          <t>-23,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -11,85</t>
+          <t>-25,13; -11,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 0,83</t>
+          <t>-11,72; 2,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,64; -2,65</t>
+          <t>-16,15; -1,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; -1,81</t>
+          <t>-12,85; 1,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,06; -28,57</t>
+          <t>-52,2; -28,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 2,79</t>
+          <t>-33,05; 9,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,43; -8,21</t>
+          <t>-39,3; -4,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,91; -8,25</t>
+          <t>-42,66; 9,29</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-5,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-24,26%</t>
+          <t>-29,18%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,18; -2,41</t>
+          <t>-20,8; -1,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -1,83</t>
+          <t>-21,01; -2,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,48; -5,44</t>
+          <t>-23,1; -4,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 0,79</t>
+          <t>-12,13; -0,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,44; -6,84</t>
+          <t>-47,25; -4,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,04; -4,65</t>
+          <t>-45,0; -6,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-52,19; -15,77</t>
+          <t>-51,31; -13,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 5,98</t>
+          <t>-49,49; -1,25</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-9,13</t>
+          <t>-9,53</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-32,81%</t>
+          <t>-33,96%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,33; -14,75</t>
+          <t>-31,01; -14,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 2,21</t>
+          <t>-14,55; 0,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 1,15</t>
+          <t>-14,75; 1,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,96; -2,99</t>
+          <t>-15,31; -3,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,37; -35,02</t>
+          <t>-62,18; -36,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,4; 8,09</t>
+          <t>-41,67; 2,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 4,15</t>
+          <t>-38,89; 5,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -11,94</t>
+          <t>-48,98; -12,99</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-9,76</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-35,15%</t>
+          <t>-13,39%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -6,72</t>
+          <t>-16,91; -5,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,63; -6,41</t>
+          <t>-16,53; -5,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 0,52</t>
+          <t>-9,91; -0,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -2,16</t>
+          <t>-8,54; 1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,21; -19,68</t>
+          <t>-42,45; -17,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -17,76</t>
+          <t>-39,82; -15,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 2,03</t>
+          <t>-30,09; 0,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,41; -8,27</t>
+          <t>-28,87; 5,64</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-10,03</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-16,22%</t>
+          <t>-38,13%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,77; -12,06</t>
+          <t>-21,55; -11,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,15; -5,99</t>
+          <t>-15,84; -5,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,24; -1,75</t>
+          <t>-11,54; -1,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 9,01</t>
+          <t>-13,8; -5,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,86; -32,56</t>
+          <t>-51,53; -32,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,19; -17,56</t>
+          <t>-40,66; -17,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,88; -6,23</t>
+          <t>-32,63; -5,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 97,01</t>
+          <t>-48,77; -24,65</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-6,6</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-26,16%</t>
+          <t>-25,82%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -13,2</t>
+          <t>-17,47; -13,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -7,62</t>
+          <t>-12,24; -7,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -6,27</t>
+          <t>-10,92; -6,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -1,31</t>
+          <t>-8,61; -4,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-42,63; -34,13</t>
+          <t>-42,89; -34,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,09; -21,53</t>
+          <t>-32,26; -21,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-30,1; -18,97</t>
+          <t>-30,31; -19,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-38,15; -7,79</t>
+          <t>-32,16; -18,44</t>
         </is>
       </c>
     </row>
